--- a/session_notes_glossary.xlsx
+++ b/session_notes_glossary.xlsx
@@ -1,155 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shalliday/Dropbox/Hopkins/Teaching/Progress/progress-fys/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A258DC0-8BAF-0540-A647-066807896F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4640" yWindow="1080" windowWidth="26340" windowHeight="15500" xr2:uid="{08C7D40D-0E26-8D4F-8B14-731DD6E9B9AF}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4640" yWindow="1080" windowWidth="26340" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>Glossary Term</t>
-  </si>
-  <si>
-    <t>Session notes glossary definition</t>
-  </si>
-  <si>
-    <t>nonrival / nonrivalry</t>
-  </si>
-  <si>
-    <t>nonexcludable</t>
-  </si>
-  <si>
-    <t>rival</t>
-  </si>
-  <si>
-    <t>public good</t>
-  </si>
-  <si>
-    <t>market failure</t>
-  </si>
-  <si>
-    <t>spillover</t>
-  </si>
-  <si>
-    <t>basic research</t>
-  </si>
-  <si>
-    <t>applied research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A good is rival when more people using
-the good reduces the benefits available to
-other users. See also nonrival. </t>
-  </si>
-  <si>
-    <t>private good</t>
-  </si>
-  <si>
-    <t>A private good is rival and
-excludable. See also common property resource,
-public good, club good</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A public good is non-rival and
-non-excludable. See also common property
-resource, private good, club good. </t>
-  </si>
-  <si>
-    <t>A good is excludable when a
-potential user may be denied access to the
-good at a low or zero cost.</t>
-  </si>
-  <si>
-    <t>excludable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A good is nonexcludable when a potential user may not be denied acess to the good at low or zero cost. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A good is nonrival when more people using
-the good does not reduce the benefits available to
-other users. See also rival. </t>
-  </si>
-  <si>
-    <t>A spillover is an external effect. An external effect occurs when a person’s action confers a
-benefit or imposes a cost on others and this cost or benefit is not taken into
-account by the individual taking the action. External effects are also called
-externalities or spillovers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When markets allocate resources in (Pareto) inefficient ways. </t>
-  </si>
-  <si>
-    <t>club good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A common
-property resource is rival and non-
-excludable. See also public good, private good,
-club good. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A club good is non-rival and
-excludable. See also common property resource,
-public good, private good. </t>
-  </si>
-  <si>
-    <t>Basic research is experimental or theoretical work undertaken to advance scientific knowledge without any particular application or use in view. Its value may only become apparent much later, and it forms the foundation on which applied research builds. See also: applied research.</t>
-  </si>
-  <si>
-    <t>Applied research is original investigation directed primarily towards a specific practical aim or objective, building on the knowledge produced by basic research. See also: basic research.</t>
-  </si>
-  <si>
-    <t>common property resource</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,30 +45,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -509,116 +445,427 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E9D76E-3B90-4640-8E2E-5B213C003CC8}">
-  <dimension ref="B1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.33203125" customWidth="1"/>
+    <col width="12.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="49.33203125" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Glossary Term</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Session notes glossary definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="51" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nonrival / nonrivalry</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A good is nonrival when more people using
+the good does not reduce the benefits available to
+other users. See also rival. </t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>excludable</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>A good is excludable when a
+potential user may be denied access to the
+good at a low or zero cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nonexcludable</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A good is nonexcludable when a potential user may not be denied acess to the good at low or zero cost. </t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A good is rival when more people using
+the good reduces the benefits available to
+other users. See also nonrival. </t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>public good</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> A public good is non-rival and
+non-excludable. See also common property
+resource, private good, club good. </t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>market failure</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>When markets allocate resources in a Pareto-inefficient way. Market failures arise from public goods (nonrival and nonexcludable goods that markets underprovide), externalities (costs or benefits not captured in market prices), and other sources. The underinvestment in basic research is a classic market failure driven by positive knowledge externalities. See also: public good, externality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="119" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>spillover</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>An external effect: a positive or negative effect of a production, consumption, or other economic decision on another person or people that is not specified as a benefit or liability in a contract. Also called an externality or external effect. Knowledge spillovers — where the benefits of basic research flow freely to others who did not fund it — are the key market failure that justifies public funding of science. See also: externality, market failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="102" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>basic research</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Basic research is experimental or theoretical work undertaken to advance scientific knowledge without any particular application or use in view. Its value may only become apparent much later, and it forms the foundation on which applied research builds. See also: applied research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="68" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>applied research</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Applied research is original investigation directed primarily towards a specific practical aim or objective, building on the knowledge produced by basic research. See also: basic research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>private good</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>A private good is rival and
+excludable. See also common property resource,
+public good, club good</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>club good</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A club good is non-rival and
+excludable. See also common property resource,
+public good, private good. </t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>common property resource</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A common
+property resource is rival and non-
+excludable. See also public good, private good,
+club good. </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>heuristic thinking</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>The use of mental shortcuts or rules of thumb to make quick judgments. Heuristics are efficient in familiar environments but prone to systematic errors when applied to unfamiliar or large-scale problems — which is why they distort our picture of global development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>negativity instinct</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Our tendency to notice bad news more readily than good news. An evolved cognitive bias that makes gradual improvements invisible while sudden setbacks feel salient. Rosling argues this instinct, combined with media bias toward dramatic events and misremembering the past, explains why most people think the world is getting worse when the data show it is getting better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>gap instinct</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>The urge to divide the world into two distinct groups with a gap between them — 'us' vs. 'them,' 'developed' vs. 'developing.' Rosling's term for the mental model that produces a false binary picture of global inequality. The gap instinct is a problem because the majority of humanity now lives in the middle, between the two old boxes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>four income levels</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Rosling's framework for replacing the developed/developing binary. Level 1: ~$1–2/day (extreme poverty, ~1 billion people). Level 2: ~$2–8/day (basic needs met with effort, ~3 billion). Level 3: ~$8–32/day (relative comfort, ~2 billion). Level 4: $32+/day (affluence, ~1 billion). Most of humanity lives on Levels 2 and 3, not Level 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>development as freedom</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Amartya Sen's framework in which development means expanding the substantive freedoms people have to live lives they have reason to value. Income growth is a means to this end, not the end itself. A country whose GDP rises while people remain unable to vote, access healthcare, or choose their occupation is not developing in the sense that matters. See also: constitutive role, instrumental role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>constitutive role of freedom</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Freedom as part of what development is, not merely a means to it. Sen's claim that being unable to vote, access healthcare, or choose one's occupation is a deprivation that matters regardless of income. Development that raises income while leaving these freedoms untouched is incomplete by definition. See also: instrumental role of freedom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>instrumental role of freedom</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Freedom as the means by which development happens. Political freedoms produce accountable governments that prevent famines; educational opportunities produce human capital; social opportunities (healthcare, literacy) enable economic participation. In Sen's framework, freedom drives development as well as constituting it. See also: constitutive role of freedom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Human Development Index (HDI)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>A composite measure of development combining GDP per capita, life expectancy, and years of education. Developed by the UN as a broader measure than income alone, on the grounds that health and education matter independently of their contribution to output. See also: Augmented Human Development Index.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Augmented Human Development Index (AHDI)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>An extension of the HDI that adds measures of political freedoms and civil liberties — the right to vote, freedom of speech, and freedom from arbitrary detention. These are the freedoms Sen calls constitutive: valuable in themselves, not merely as instruments of growth. The AHDI captures what standard income or HDI measures hide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>institutions</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>The laws and informal rules that regulate social interactions among people and between people and the biosphere, sometimes also termed the rules of the game. Secure institutions — including property rights, rule of law, and contract enforcement — are a necessary condition for the sustained growth capitalism requires. See also: capitalism, markets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>markets</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>The arrangements through which buyers and sellers interact to exchange goods and services. Markets coordinate economic activity through prices, giving producers incentives to supply what consumers demand. A key institution of capitalism, but one that can fail when goods have public good properties or when externalities are present. See also: market failure, public good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>capitalism</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>An economic system in which the main form of economic organization is the firm, in which the private owners of capital goods hire labour to produce goods and services for sale on markets with the intention of making a profit. UOE Chapter 3 identifies capitalism as the institutional cause of the Great Enrichment after 1800: by allowing firms to capture innovation rents, it created for the first time a sustained incentive to search for better ways of doing things. See also: innovation rent, creative destruction, institutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>innovation rent</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Profits in excess of the opportunity cost of capital that an innovator gets by introducing a new technology, organizational form, or marketing strategy. Also known as: Schumpeterian rent. Because these profits exist, firms have an incentive to search for innovations — and once competitors copy the innovation, the rent disappears, pushing firms to find the next one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>creative destruction</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Joseph Schumpeter's name for the process by which old technologies and the firms that do not adapt are swept away by the new, because they cannot compete in the market. It is 'creative' because it generates better products and methods; 'destruction' because it eliminates existing businesses and jobs. Central to capitalism because profit-seeking innovation continuously renders older methods obsolete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>economic growth</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>An increase in the total output of an economy over time, typically measured as growth in real GDP per capita. Economic growth is a necessary but not sufficient condition for development: it raises average living standards but does not guarantee that freedoms expand, inequality falls, or that the gains are broadly shared. See also: development as freedom, inequality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>inequality</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Differences among members of a society in some economic attribute such as wealth, income, or wages. Commonly measured using the Gini coefficient (where 0 = perfect equality and 1 = maximum inequality) or income shares (e.g., the share of income going to the top 1%). Capitalism produces growth but also inequality: the same system that raised average living standards created winners and losers at every stage of the process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>externality</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>A positive or negative effect of a production, consumption, or other economic decision on another person or people that is not specified as a benefit or liability in a contract. It is also called an external effect or spillover. Positive externalities (such as knowledge spillovers from basic research) lead markets to undersupply the good; negative externalities (such as pollution) lead markets to oversupply it. See also: market failure, spillover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>hockey stick (economic history)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>The shape of the GDP per capita graph over the past millennium: flat or barely growing for most of human history, then rising sharply after about 1800. The kink marks the beginning of sustained compound growth driven by capitalist institutions. The Great Enrichment is the historical content of the hockey stick shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>norms of open science</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>The expectations governing scientific community behavior: results are published, methods are disclosed, and priority (recognition) goes to whoever publishes first. These norms look strange from a private-profit perspective — why give away discoveries? — but they are a collective solution to the public goods problem: because scientists compete for priority rather than secrecy, knowledge accumulates as a public good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>division of labor</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>The specialization of tasks among workers or institutions, each focusing on what they do best. Adam Smith's pin factory is the canonical example: workers who each do one step produce far more than workers who each do all steps. In Bush's model of science policy, the division of labor assigns basic research to universities and commercial development to firms.</t>
+        </is>
       </c>
     </row>
   </sheetData>
